--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
   <si>
     <t>(name)</t>
   </si>
@@ -31,6 +31,9 @@
     <t>ItemType</t>
   </si>
   <si>
+    <t>ItemUseType</t>
+  </si>
+  <si>
     <t>MaxStack</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
   </si>
   <si>
     <t>Crop</t>
+  </si>
+  <si>
+    <t>Consumeable</t>
   </si>
   <si>
     <t>Icon_Crop_Tomato</t>
@@ -431,12 +437,15 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -459,71 +468,81 @@
       <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2">
         <v>1.0</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2">
         <v>1.0</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="G5" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="6">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="6">
         <v>1.0</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="7"/>
+      <c r="G6" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -546,102 +565,117 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2">
+        <v>99.0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" s="2">
-        <v>99.0</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="E8" s="2">
         <v>99.0</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="2">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="2">
         <v>99.0</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="2">
+        <v>30</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="2">
         <v>99.0</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="2">
+        <v>40</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="2">
         <v>50.0</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
   <si>
     <t>(name)</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>PrefabKey</t>
+  </si>
+  <si>
     <t>Item_Tool_Hoe_01</t>
   </si>
   <si>
@@ -52,7 +55,7 @@
     <t>Tool</t>
   </si>
   <si>
-    <t>Sheet_Items[Icon_Tool_Hoe_01]</t>
+    <t>Sheet_Tool[Icon_Tool_Hoe_01]</t>
   </si>
   <si>
     <t>낡고 오래된 기본 괭이</t>
@@ -64,7 +67,7 @@
     <t>낡은 물뿌리개</t>
   </si>
   <si>
-    <t>Sheet_Items[Icon_Tool_Wateringcan_01]</t>
+    <t>Sheet_Tool[Icon_Tool_Wateringcan_01]</t>
   </si>
   <si>
     <t>낡고 오래된 기본 물뿌리개</t>
@@ -76,12 +79,24 @@
     <t>낡은 도끼</t>
   </si>
   <si>
-    <t>Sheet_Items[Icon_Tool_Axe_01]</t>
+    <t>Sheet_Tool[Icon_Tool_Axe_01]</t>
   </si>
   <si>
     <t>낡고 오래된 기본 도끼</t>
   </si>
   <si>
+    <t>Item_Tool_Pickaxe_01</t>
+  </si>
+  <si>
+    <t>낡은 곡괭이</t>
+  </si>
+  <si>
+    <t>Icon_Tool_Pickaxe_01</t>
+  </si>
+  <si>
+    <t>낡고 오래된 기본 곡괭이</t>
+  </si>
+  <si>
     <t>Item_Crop_Tomato</t>
   </si>
   <si>
@@ -137,6 +152,24 @@
   </si>
   <si>
     <t>Icon_Food_GrilledTomato</t>
+  </si>
+  <si>
+    <t>Item_Furniture_Chest</t>
+  </si>
+  <si>
+    <t>상자</t>
+  </si>
+  <si>
+    <t>Furniture</t>
+  </si>
+  <si>
+    <t>Interactable</t>
+  </si>
+  <si>
+    <t>Sheet_Chest[Icon_Furniture_Chest]</t>
+  </si>
+  <si>
+    <t>기본 나무 상자</t>
   </si>
 </sst>
 </file>
@@ -448,6 +481,9 @@
       <c r="G2" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="H2" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
@@ -471,77 +507,79 @@
       <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2">
         <v>1.0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2">
         <v>1.0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="6">
         <v>1.0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -564,27 +602,46 @@
       <c r="Z6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>25</v>
       </c>
+      <c r="C7" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="2">
-        <v>99.0</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
@@ -597,13 +654,13 @@
         <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2">
         <v>99.0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>29</v>
@@ -611,71 +668,117 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2">
         <v>99.0</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2">
         <v>99.0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2">
+        <v>99.0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="2">
         <v>50.0</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>39</v>
+      <c r="F12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="59">
   <si>
     <t>(name)</t>
   </si>
@@ -37,6 +37,9 @@
     <t>MaxStack</t>
   </si>
   <si>
+    <t>ToolCategory</t>
+  </si>
+  <si>
     <t>IconKey</t>
   </si>
   <si>
@@ -55,6 +58,9 @@
     <t>Tool</t>
   </si>
   <si>
+    <t>Hoe</t>
+  </si>
+  <si>
     <t>Sheet_Tool[Icon_Tool_Hoe_01]</t>
   </si>
   <si>
@@ -67,6 +73,9 @@
     <t>낡은 물뿌리개</t>
   </si>
   <si>
+    <t>Wateringcan</t>
+  </si>
+  <si>
     <t>Sheet_Tool[Icon_Tool_Wateringcan_01]</t>
   </si>
   <si>
@@ -79,6 +88,9 @@
     <t>낡은 도끼</t>
   </si>
   <si>
+    <t>Axe</t>
+  </si>
+  <si>
     <t>Sheet_Tool[Icon_Tool_Axe_01]</t>
   </si>
   <si>
@@ -91,6 +103,9 @@
     <t>낡은 곡괭이</t>
   </si>
   <si>
+    <t>Pickaxe</t>
+  </si>
+  <si>
     <t>Icon_Tool_Pickaxe_01</t>
   </si>
   <si>
@@ -170,6 +185,9 @@
   </si>
   <si>
     <t>기본 나무 상자</t>
+  </si>
+  <si>
+    <t>Chest</t>
   </si>
 </sst>
 </file>
@@ -484,6 +502,9 @@
       <c r="H2" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="I2" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
@@ -510,78 +531,88 @@
       <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="4"/>
+      <c r="I3" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="J3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2">
         <v>1.0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2">
         <v>1.0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="6">
         <v>1.0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="7"/>
+        <v>26</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -603,27 +634,29 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="6">
         <v>1.0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -645,140 +678,143 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2">
         <v>99.0</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2">
         <v>99.0</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2">
         <v>99.0</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2">
         <v>99.0</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2">
         <v>50.0</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2">
         <v>50.0</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="G13" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/85867b8a770c3dbd/문서/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="71" documentId="8_{7D93D76A-8061-4EB0-90A6-7C01A1D4BA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{658B4C3C-5A37-4EA0-ACCE-922C864383BB}"/>
+  <bookViews>
+    <workbookView xWindow="-21816" yWindow="1968" windowWidth="21108" windowHeight="11592" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
+    <sheet name="시트1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="84">
   <si>
     <t>(name)</t>
   </si>
@@ -124,9 +133,6 @@
     <t>Consumeable</t>
   </si>
   <si>
-    <t>Icon_Crop_Tomato</t>
-  </si>
-  <si>
     <t>Item_Seed_Tomato</t>
   </si>
   <si>
@@ -136,27 +142,18 @@
     <t>Seed</t>
   </si>
   <si>
-    <t>Icon_Seed_Tomato</t>
-  </si>
-  <si>
     <t>Item_Crop_Potato</t>
   </si>
   <si>
     <t>감자</t>
   </si>
   <si>
-    <t>Icon_Crop_Potato</t>
-  </si>
-  <si>
     <t>Item_Seed_Potato</t>
   </si>
   <si>
     <t>감자 씨앗</t>
   </si>
   <si>
-    <t>Icon_Seed_Potato</t>
-  </si>
-  <si>
     <t>Item_Food_GriiledTomato</t>
   </si>
   <si>
@@ -188,22 +185,240 @@
   </si>
   <si>
     <t>Chest</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuyPrice</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SellPrice</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Drop_Log</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>통나무</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Drop_Cobble</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조약돌</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Crop_Carrot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Seed_Carrot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Crop_Strawberry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Seed_Stawberry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>딸기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>딸기 씨앗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>당근</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>씨앗</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>당근</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>딸기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>씨앗</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sheet_Tomato[Icon_Crop_Tomato]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sheet_Tomato[Icon_Seed_Tomato]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sheet_Potato[Icon_Crop_Potato]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sheet_Potato[Icon_Seed_Potato]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sheet_Carrot[Icon_Crop_Carrot]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sheet_Carrot[Icon_Seed_Carrot]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sheet_Strawberry[Icon_Crop_Strawberry]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sheet_Strawberry[Icon_Seed_Strawberry]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>material</t>
+  </si>
+  <si>
+    <t>material</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drop</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Drop_Log</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Drop_Cobble</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -212,7 +427,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -222,52 +437,51 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -457,367 +671,556 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z19"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.5"/>
-    <col customWidth="1" min="3" max="3" width="12.63"/>
-    <col customWidth="1" min="5" max="5" width="21.13"/>
-    <col customWidth="1" min="6" max="6" width="19.25"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="37.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="J2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="J3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="s">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="2">
-        <v>99.0</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="E8" s="1">
+        <v>99</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="1">
+        <v>99</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="2">
-        <v>99.0</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="E10" s="1">
+        <v>99</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="K10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="D11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="1">
+        <v>99</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="J11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="1">
+        <v>50</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="2">
-        <v>99.0</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E13" s="1">
+        <v>99</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="2">
-        <v>99.0</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="E14" s="1">
+        <v>99</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="1">
+        <v>99</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="K15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="1">
+        <v>99</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="2">
-        <v>50.0</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="E17" s="1">
+        <v>50</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="H17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="I17" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="2">
-        <v>50.0</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I13" s="2" t="s">
+    </row>
+    <row r="18" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="B18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="1">
+        <v>99</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="1">
+        <v>99</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="K19">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>